--- a/outputs/model_vecm/model_vecm_output.xlsx
+++ b/outputs/model_vecm/model_vecm_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,231 +436,97 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>retailer</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>y_series_source</t>
+          <t>promo_variant</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>x_series_sources</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>link</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>sample_period</t>
+          <t>model_family</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>lags_selected</t>
+          <t>y_series</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>cointegration_rank</t>
+          <t>x_series</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>cointegration_vectors</t>
+          <t>n_obs</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>adjustment_alpha_abs_mean</t>
+          <t>sr_coef</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>diagnostics_flags</t>
+          <t>lr_coef</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>interpretation_note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>hard_cheese</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>System A</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ProducerUA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ConsumerUA, EU</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2021-12-28..2025-12-23</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>k_ar_diff=3</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1.000; -0.643; -0.104</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.6905463602735168</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>VECM estimated</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Rank&gt;0 supports long-run co-movement in the system.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>milk</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>System A</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ProducerUA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ConsumerUA, EU</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2021-12-28..2025-12-23</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>k_ar_diff=3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1.000; 0.000; 0.000</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.07202042647366828</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>VECM estimated</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Rank&gt;0 supports long-run co-movement in the system.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>milk</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>System D</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ProducerUA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>EU, CME</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2021-12-28..2025-12-23</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>k_ar_diff=3</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1.000; -0.000; 0.000</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.06026866786576559</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>VECM estimated</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Rank&gt;0 supports long-run co-movement in the system.</t>
+          <t>ect_coef</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ect_pvalue</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>asymmetry_short_p</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>asymmetry_long_p</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>vecm_rank</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>model_status</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>unreliable_flag</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>primary_chain_doc</t>
         </is>
       </c>
     </row>
